--- a/docs/jours-destinations.xlsx
+++ b/docs/jours-destinations.xlsx
@@ -1,64 +1,165 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
   <workbookPr/>
-  <workbookProtection/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/27d5916ca408fb47/Documents/Projets_Python/Application de voyage familiale/docs/"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="22" documentId="11_A14B3EE0D2DE4A1BCF98E85C414BE29C9415B1C6" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{92308898-E5AD-4665-8512-AE2B5F6809BB}"/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="jours-destinations" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="jours-destinations" sheetId="1" r:id="rId1"/>
   </sheets>
-  <definedNames/>
-  <calcPr calcId="124519" fullCalcOnLoad="1"/>
+  <calcPr calcId="0"/>
 </workbook>
 </file>
 
+<file path=xl/comments1.xml><?xml version="1.0" encoding="utf-8"?>
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
+  <authors>
+    <author>Guide</author>
+  </authors>
+  <commentList>
+    <comment ref="A1" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000001000000}">
+      <text>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color theme="1"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+            <scheme val="minor"/>
+          </rPr>
+          <t>Colonne numérique utilisée pour calculer le jour actuel du voyage (story 14.1). Ne pas y mettre autre chose qu'un entier.</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="C1" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000002000000}">
+      <text>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color theme="1"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+            <scheme val="minor"/>
+          </rPr>
+          <t>Texte libre. Vous pouvez ajouter d'autres colonnes à droite (ex: notes, horaires) : l'application ignore les colonnes qu'elle ne connaît pas, elle ne plantera pas.</t>
+        </r>
+      </text>
+    </comment>
+  </commentList>
+</comments>
+</file>
+
+<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="23" uniqueCount="17">
+  <si>
+    <t>jour</t>
+  </si>
+  <si>
+    <t>destination</t>
+  </si>
+  <si>
+    <t>visites_prevues</t>
+  </si>
+  <si>
+    <t>Istanbul</t>
+  </si>
+  <si>
+    <t>Cappadoce</t>
+  </si>
+  <si>
+    <t>Pamukkale</t>
+  </si>
+  <si>
+    <t>Site d'Éphèse</t>
+  </si>
+  <si>
+    <t>Izmir</t>
+  </si>
+  <si>
+    <t>Bursa</t>
+  </si>
+  <si>
+    <t>Légende</t>
+  </si>
+  <si>
+    <t>Cellules en jaune pâle : à éditer librement (jour, destination, visites prévues).</t>
+  </si>
+  <si>
+    <t>Le lien avec les lieux détaillés (photos, histoire...) se fait séparément dans places.ts via le champ "jour".</t>
+  </si>
+  <si>
+    <t>Pour ajouter un jour : ajoutez simplement une nouvelle ligne avec le numéro suivant.</t>
+  </si>
+  <si>
+    <t>Turquie</t>
+  </si>
+  <si>
+    <t>Voyage en avion : Nantes, Paris, Toulouse</t>
+  </si>
+  <si>
+    <t>Sainte-Sophie, Citerne Basilique, Kadikoï, Le Bosphore</t>
+  </si>
+  <si>
+    <t>Mosquée Bleue, Place Taksim, Quartier de Péra</t>
+  </si>
+</sst>
+</file>
+
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
-  <fonts count="5">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="5" x14ac:knownFonts="1">
     <font>
+      <sz val="11"/>
+      <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
-      <color theme="1"/>
-      <sz val="11"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <name val="Arial"/>
-      <b val="1"/>
-      <color rgb="00FFFFFF"/>
-    </font>
-    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
       <name val="Arial"/>
     </font>
     <font>
+      <sz val="11"/>
       <name val="Arial"/>
-      <b val="1"/>
-      <i val="1"/>
     </font>
     <font>
+      <b/>
+      <i/>
+      <sz val="11"/>
       <name val="Arial"/>
-      <i val="1"/>
+    </font>
+    <font>
+      <i/>
       <sz val="9"/>
+      <name val="Arial"/>
     </font>
   </fonts>
   <fills count="4">
     <fill>
-      <patternFill/>
+      <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="002F8F80"/>
+        <fgColor rgb="FF2F8F80"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00FFF9E0"/>
+        <fgColor rgb="FFFFF9E0"/>
       </patternFill>
     </fill>
   </fills>
@@ -75,107 +176,28 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
   <cellXfs count="5">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
+  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
-  <colors>
-    <indexedColors>
-      <rgbColor rgb="00000000"/>
-      <rgbColor rgb="00FFFFFF"/>
-      <rgbColor rgb="00FF0000"/>
-      <rgbColor rgb="0000FF00"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00000000"/>
-      <rgbColor rgb="00FFFFFF"/>
-      <rgbColor rgb="00FF0000"/>
-      <rgbColor rgb="0000FF00"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00800000"/>
-      <rgbColor rgb="00008000"/>
-      <rgbColor rgb="00000080"/>
-      <rgbColor rgb="00808000"/>
-      <rgbColor rgb="00800080"/>
-      <rgbColor rgb="00008080"/>
-      <rgbColor rgb="00C0C0C0"/>
-      <rgbColor rgb="00808080"/>
-      <rgbColor rgb="009999FF"/>
-      <rgbColor rgb="00993366"/>
-      <rgbColor rgb="00FFFFCC"/>
-      <rgbColor rgb="00CCFFFF"/>
-      <rgbColor rgb="00660066"/>
-      <rgbColor rgb="00FF8080"/>
-      <rgbColor rgb="000066CC"/>
-      <rgbColor rgb="00CCCCFF"/>
-      <rgbColor rgb="00000080"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00800080"/>
-      <rgbColor rgb="00800000"/>
-      <rgbColor rgb="00008080"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="0000CCFF"/>
-      <rgbColor rgb="00CCFFFF"/>
-      <rgbColor rgb="00CCFFCC"/>
-      <rgbColor rgb="00FFFF99"/>
-      <rgbColor rgb="0099CCFF"/>
-      <rgbColor rgb="00FF99CC"/>
-      <rgbColor rgb="00CC99FF"/>
-      <rgbColor rgb="00FFCC99"/>
-      <rgbColor rgb="003366FF"/>
-      <rgbColor rgb="0033CCCC"/>
-      <rgbColor rgb="0099CC00"/>
-      <rgbColor rgb="00FFCC00"/>
-      <rgbColor rgb="00FF9900"/>
-      <rgbColor rgb="00FF6600"/>
-      <rgbColor rgb="00666699"/>
-      <rgbColor rgb="00969696"/>
-      <rgbColor rgb="00003366"/>
-      <rgbColor rgb="00339966"/>
-      <rgbColor rgb="00003300"/>
-      <rgbColor rgb="00333300"/>
-      <rgbColor rgb="00993300"/>
-      <rgbColor rgb="00993366"/>
-      <rgbColor rgb="00333399"/>
-      <rgbColor rgb="00333333"/>
-    </indexedColors>
-  </colors>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
-</file>
-
-<file path=xl/comments/comment1.xml><?xml version="1.0" encoding="utf-8"?>
-<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <authors>
-    <author>Guide</author>
-  </authors>
-  <commentList>
-    <comment ref="A1" authorId="0" shapeId="0">
-      <text>
-        <t>Colonne numérique utilisée pour calculer le jour actuel du voyage (story 14.1). Ne pas y mettre autre chose qu'un entier.</t>
-      </text>
-    </comment>
-    <comment ref="C1" authorId="0" shapeId="0">
-      <text>
-        <t>Texte libre. Vous pouvez ajouter d'autres colonnes à droite (ex: notes, horaires) : l'application ignore les colonnes qu'elle ne connaît pas, elle ne plantera pas.</t>
-      </text>
-    </comment>
-  </commentList>
-</comments>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -462,156 +484,136 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:C13"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="A1:C15"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col width="8" customWidth="1" min="1" max="1"/>
-    <col width="22" customWidth="1" min="2" max="2"/>
-    <col width="40" customWidth="1" min="3" max="3"/>
+    <col min="1" max="1" width="8" customWidth="1"/>
+    <col min="2" max="2" width="22" customWidth="1"/>
+    <col min="3" max="3" width="52" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>jour</t>
-        </is>
-      </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>destination</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>visites_prevues</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" s="2" t="n">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="2" t="inlineStr">
-        <is>
-          <t>Istanbul</t>
-        </is>
-      </c>
-      <c r="C2" s="2" t="inlineStr">
-        <is>
-          <t>Istanbul, Palais de Topkapi</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="2" t="n">
+      <c r="C1" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="B3" s="2" t="inlineStr">
-        <is>
-          <t>Cappadoce</t>
-        </is>
-      </c>
-      <c r="C3" s="2" t="inlineStr">
-        <is>
-          <t>Cappadoce</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="2" t="n">
+    </row>
+    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A2" s="2">
+        <v>1</v>
+      </c>
+      <c r="B2" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="C2" s="2" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A3" s="2">
+        <v>2</v>
+      </c>
+      <c r="B3" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="B4" s="2" t="inlineStr">
-        <is>
-          <t>Pamukkale</t>
-        </is>
-      </c>
-      <c r="C4" s="2" t="inlineStr">
-        <is>
-          <t>Pamukkale</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="2" t="n">
+      <c r="C3" s="2" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A4" s="2">
+        <v>3</v>
+      </c>
+      <c r="B4" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="C4" s="2" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A5" s="2">
         <v>4</v>
       </c>
-      <c r="B5" s="2" t="inlineStr">
-        <is>
-          <t>Site d'Éphèse</t>
-        </is>
-      </c>
-      <c r="C5" s="2" t="inlineStr">
-        <is>
-          <t>Site d'Éphèse</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="2" t="n">
+      <c r="B5" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="C5" s="2" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A6" s="2">
         <v>5</v>
       </c>
-      <c r="B6" s="2" t="inlineStr">
-        <is>
-          <t>Izmir</t>
-        </is>
-      </c>
-      <c r="C6" s="2" t="inlineStr">
-        <is>
-          <t>Izmir</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="2" t="n">
+      <c r="B6" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C6" s="2" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A7" s="2">
         <v>6</v>
       </c>
-      <c r="B7" s="2" t="inlineStr">
-        <is>
-          <t>Bursa</t>
-        </is>
-      </c>
-      <c r="C7" s="2" t="inlineStr">
-        <is>
-          <t>Bursa</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="3" t="inlineStr">
-        <is>
-          <t>Légende</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="4" t="inlineStr">
-        <is>
-          <t>Cellules en jaune pâle : à éditer librement (jour, destination, visites prévues).</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="4" t="inlineStr">
-        <is>
-          <t>Le lien avec les lieux détaillés (photos, histoire...) se fait séparément dans places.ts via le champ "jour".</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="4" t="inlineStr">
-        <is>
-          <t>Pour ajouter un jour : ajoutez simplement une nouvelle ligne avec le numéro suivant.</t>
-        </is>
+      <c r="B7" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="C7" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A8" s="2">
+        <v>7</v>
+      </c>
+      <c r="B8" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="C8" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A9" s="2">
+        <v>8</v>
+      </c>
+      <c r="B9" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="C9" s="2" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="12" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A12" s="3" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="13" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A13" s="4" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="14" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A14" s="4" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="15" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A15" s="4" t="s">
+        <v>12</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <legacyDrawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="anysvml"/>
+  <legacyDrawing r:id="rId1"/>
 </worksheet>
 </file>
--- a/docs/jours-destinations.xlsx
+++ b/docs/jours-destinations.xlsx
@@ -8,14 +8,27 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/27d5916ca408fb47/Documents/Projets_Python/Application de voyage familiale/docs/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="22" documentId="11_A14B3EE0D2DE4A1BCF98E85C414BE29C9415B1C6" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{92308898-E5AD-4665-8512-AE2B5F6809BB}"/>
+  <xr:revisionPtr revIDLastSave="33" documentId="11_A14B3EE0D2DE4A1BCF98E85C414BE29C9415B1C6" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{52F91907-23BB-47B4-AFB2-6E8EC42BBE20}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="jours-destinations" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="0"/>
+  <calcPr calcId="191029"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
@@ -102,13 +115,13 @@
     <t>Turquie</t>
   </si>
   <si>
-    <t>Voyage en avion : Nantes, Paris, Toulouse</t>
-  </si>
-  <si>
     <t>Sainte-Sophie, Citerne Basilique, Kadikoï, Le Bosphore</t>
   </si>
   <si>
     <t>Mosquée Bleue, Place Taksim, Quartier de Péra</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> </t>
   </si>
 </sst>
 </file>
@@ -198,6 +211,10 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -485,7 +502,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:C15"/>
+  <dimension ref="A1:D15"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="8" customWidth="1"/>
@@ -493,7 +510,7 @@
     <col min="3" max="3" width="52" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -504,7 +521,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A2" s="2">
         <v>1</v>
       </c>
@@ -512,10 +529,14 @@
         <v>13</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
+        <v>16</v>
+      </c>
+      <c r="D2" t="str">
+        <f>CONCATENATE(A2,",",B2,",","'",C2,"'")</f>
+        <v>1,Turquie,' '</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A3" s="2">
         <v>2</v>
       </c>
@@ -523,10 +544,14 @@
         <v>3</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
+        <v>14</v>
+      </c>
+      <c r="D3" t="str">
+        <f>CONCATENATE(A3,",",B3,",","'",C3,"'")</f>
+        <v>2,Istanbul,'Sainte-Sophie, Citerne Basilique, Kadikoï, Le Bosphore'</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A4" s="2">
         <v>3</v>
       </c>
@@ -534,10 +559,14 @@
         <v>3</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
+        <v>15</v>
+      </c>
+      <c r="D4" t="str">
+        <f t="shared" ref="D4:D9" si="0">CONCATENATE(A4,",",B4,",","'",C4,"'")</f>
+        <v>3,Istanbul,'Mosquée Bleue, Place Taksim, Quartier de Péra'</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A5" s="2">
         <v>4</v>
       </c>
@@ -547,8 +576,12 @@
       <c r="C5" s="2" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D5" t="str">
+        <f t="shared" si="0"/>
+        <v>4,Cappadoce,'Cappadoce'</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A6" s="2">
         <v>5</v>
       </c>
@@ -558,8 +591,12 @@
       <c r="C6" s="2" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D6" t="str">
+        <f t="shared" si="0"/>
+        <v>5,Pamukkale,'Pamukkale'</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A7" s="2">
         <v>6</v>
       </c>
@@ -569,8 +606,12 @@
       <c r="C7" s="2" t="s">
         <v>6</v>
       </c>
-    </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D7" t="str">
+        <f t="shared" si="0"/>
+        <v>6,Site d'Éphèse,'Site d'Éphèse'</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A8" s="2">
         <v>7</v>
       </c>
@@ -580,8 +621,12 @@
       <c r="C8" s="2" t="s">
         <v>7</v>
       </c>
-    </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D8" t="str">
+        <f t="shared" si="0"/>
+        <v>7,Izmir,'Izmir'</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A9" s="2">
         <v>8</v>
       </c>
@@ -591,23 +636,27 @@
       <c r="C9" s="2" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D9" t="str">
+        <f t="shared" si="0"/>
+        <v>8,Bursa,'Bursa'</v>
+      </c>
+    </row>
+    <row r="12" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A12" s="3" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="13" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A13" s="4" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="14" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A14" s="4" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="15" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A15" s="4" t="s">
         <v>12</v>
       </c>
